--- a/ET/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -92,7 +92,7 @@
     <t>0,0,1000,1200,1300</t>
   </si>
   <si>
-    <t>100103,100101,100102,100104</t>
+    <t>100103,100101,100102,100105</t>
   </si>
 </sst>
 </file>
